--- a/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
@@ -345,7 +345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1683,7 +1683,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">ahead.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1708,14 +1708,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参ったわね。でも…忘れないわよ</t>
+          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">behind.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1740,14 +1740,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅ。やっと終わったわね。もう勘弁して</t>
+          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。…でも笑えるわ。最高の相手だもの</t>
+          <t xml:space="preserve">…参ったわね。でも…忘れないわよ</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相手だったわ。…これからもよろしくね</t>
+          <t xml:space="preserve">…ふぅ。やっと終わったわね。もう勘弁して</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1836,14 +1836,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いよいよね。…全部出し切るわ</t>
+          <t xml:space="preserve">負けちゃった。…でも笑えるわ。最高の相手だもの</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1868,14 +1868,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ。全力で受けて立つわ</t>
+          <t xml:space="preserve">最高の相手だったわ。…これからもよろしくね</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
@@ -1900,14 +1900,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ようやく、この日ね。全部、出し切るわ</t>
+          <t xml:space="preserve">いよいよね。…全部出し切るわ</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ。言葉は、いらないわね</t>
+          <t xml:space="preserve">いいわよ。全力で受けて立つわ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
@@ -1964,14 +1964,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さーて、決着ね。全部出し切ってあげるわ</t>
+          <t xml:space="preserve">……ようやく、この日ね。全部、出し切るわ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
@@ -1996,14 +1996,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいわよ、来なさい。相手してあげるわ</t>
+          <t xml:space="preserve">……ええ。言葉は、いらないわね</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">attacker.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦ね。…全部出し切るわ</t>
+          <t xml:space="preserve">さーて、決着ね。全部出し切ってあげるわ</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defender.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の締めにしましょう？ …全力でね</t>
+          <t xml:space="preserve">いいわよ、来なさい。相手してあげるわ</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、負けちゃった。…でも次は覚悟しておいてね</t>
+          <t xml:space="preserve">最後の一戦ね。…全部出し切るわ</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとつ勝ち。ふふ…でもまだこれからよ</t>
+          <t xml:space="preserve">最高の締めにしましょう？ …全力でね</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loserLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわ〜…でもね、次は覚悟してね？</t>
+          <t xml:space="preserve">あら、負けちゃった。…でも次は覚悟しておいてね</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2188,14 +2188,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった〜。…でもね、まだ終わってない気がするの</t>
+          <t xml:space="preserve">ひとつ勝ち。ふふ…でもまだこれからよ</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2220,14 +2220,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ…嘘でしょう…まさか…</t>
+          <t xml:space="preserve">負けちゃったわ〜…でもね、次は覚悟してね？</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそ…勝っちゃった…ふふ、信じられない</t>
+          <t xml:space="preserve">勝っちゃった〜。…でもね、まだ終わってない気がするの</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2269,29 +2269,29 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.lose[1]</t>
+          <t xml:space="preserve">loserLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。……悔しい、けっこう悔しい。</t>
+          <t xml:space="preserve">えっ…嘘でしょう…まさか…</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.lose[2]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2301,29 +2301,29 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.lose[2]</t>
+          <t xml:space="preserve">winnerLines.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">だめだったわ。……ごめん、社長。堪えたわ。</t>
+          <t xml:space="preserve">うそ…勝っちゃった…ふふ、信じられない</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.lose[3]</t>
+          <t xml:space="preserve">seductive_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2348,14 +2348,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたの。……ふふ、笑えないわね、これは。</t>
+          <t xml:space="preserve">負けちゃった。……悔しい、けっこう悔しい。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.petition[1]</t>
+          <t xml:space="preserve">seductive_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2380,14 +2380,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、あの人とやりたいの。だめ?</t>
+          <t xml:space="preserve">だめだったわ。……ごめん、社長。堪えたわ。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.petition[2]</t>
+          <t xml:space="preserve">seductive_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2412,14 +2412,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ社長、あの人と当てて。お願い。</t>
+          <t xml:space="preserve">負けたの。……ふふ、笑えないわね、これは。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.petition[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.petition[3]</t>
+          <t xml:space="preserve">seductive_easygoing.petition[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とやらせて? わがままよね、私。</t>
+          <t xml:space="preserve">社長〜、あの人とやりたいの。だめ?</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.petition[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.sendoff[1]</t>
+          <t xml:space="preserve">seductive_easygoing.petition[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった。ありがと、社長。行ってくるわ。</t>
+          <t xml:space="preserve">ねえ社長、あの人と当てて。お願い。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.petition[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.sendoff[2]</t>
+          <t xml:space="preserve">seductive_easygoing.petition[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2508,14 +2508,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、通っちゃった。感謝するわ。</t>
+          <t xml:space="preserve">あの人とやらせて? わがままよね、私。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.sendoff[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.sendoff[3]</t>
+          <t xml:space="preserve">seductive_easygoing.sendoff[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2540,14 +2540,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがと。ちゃんと勝ってくるから。</t>
+          <t xml:space="preserve">やった。ありがと、社長。行ってくるわ。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.sendoff[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.win[1]</t>
+          <t xml:space="preserve">seductive_easygoing.sendoff[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2572,14 +2572,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。ふふ、ありがと社長。</t>
+          <t xml:space="preserve">ふふ、通っちゃった。感謝するわ。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.sendoff[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.win[2]</t>
+          <t xml:space="preserve">seductive_easygoing.sendoff[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったわよ。頷いてくれて、よかった。</t>
+          <t xml:space="preserve">ありがと。ちゃんと勝ってくるから。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.win[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.win[3]</t>
+          <t xml:space="preserve">seductive_easygoing.win[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほら、いい報告。ありがとね、社長。</t>
+          <t xml:space="preserve">勝っちゃった。ふふ、ありがと社長。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.win[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing._accept[1]</t>
+          <t xml:space="preserve">seductive_easygoing.win[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2668,14 +2668,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、私? ふふ、いいわよー、遊びましょ。</t>
+          <t xml:space="preserve">勝ったわよ。頷いてくれて、よかった。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.seductive_easygoing.win[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing._accept[2]</t>
+          <t xml:space="preserve">seductive_easygoing.win[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2700,14 +2700,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、呼ばれたら行くわよ。そういうものでしょ?</t>
+          <t xml:space="preserve">ほら、いい報告。ありがとね、社長。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing._accept[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing._accept[3]</t>
+          <t xml:space="preserve">seductive_easygoing._accept[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2732,14 +2732,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、断るの面倒だし。…受けるわ。</t>
+          <t xml:space="preserve">え、私? ふふ、いいわよー、遊びましょ。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing._accept[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.draw[1]</t>
+          <t xml:space="preserve">seductive_easygoing._accept[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2764,14 +2764,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けかぁ。…ま、いいんじゃない?</t>
+          <t xml:space="preserve">ま、呼ばれたら行くわよ。そういうものでしょ?</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing._accept[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.draw[2]</t>
+          <t xml:space="preserve">seductive_easygoing._accept[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2796,14 +2796,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決まらなかったわね。お茶でも飲む?</t>
+          <t xml:space="preserve">あら、断るの面倒だし。…受けるわ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.draw[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.draw[3]</t>
+          <t xml:space="preserve">seductive_easygoing.draw[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2828,14 +2828,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、しつこいんだから。ふふ。</t>
+          <t xml:space="preserve">決着つかずかぁ。…ま、いいんじゃない?</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.draw[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.lose[1]</t>
+          <t xml:space="preserve">seductive_easygoing.draw[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、やられちゃった。ふふ。</t>
+          <t xml:space="preserve">決まらなかったわね。お茶でも飲む?</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.draw[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.lose[2]</t>
+          <t xml:space="preserve">seductive_easygoing.draw[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2892,14 +2892,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こういう日もあるわよね。</t>
+          <t xml:space="preserve">もう、しつこいんだから。ふふ。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.lose[3]</t>
+          <t xml:space="preserve">seductive_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2924,14 +2924,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……ことにしておくわ。</t>
+          <t xml:space="preserve">あらら、やられちゃった。ふふ。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.win[1]</t>
+          <t xml:space="preserve">seductive_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2956,14 +2956,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、勝っちゃった。ごめんね?</t>
+          <t xml:space="preserve">まあ、こういう日もあるわよね。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.win[2]</t>
+          <t xml:space="preserve">seductive_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2988,14 +2988,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんまり気張らないの。…疲れるわよ。</t>
+          <t xml:space="preserve">悔しい……ことにしておくわ。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.win[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive_easygoing.win[3]</t>
+          <t xml:space="preserve">seductive_easygoing.win[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -3020,14 +3020,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ね、思ったより楽しかったわ。</t>
+          <t xml:space="preserve">ふふ、勝っちゃった。ごめんね?</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.win[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3037,29 +3037,29 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive_easygoing.win[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しやってみようかしら</t>
+          <t xml:space="preserve">あんまり気張らないの。…疲れるわよ。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.seductive_easygoing.win[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3069,29 +3069,29 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive_easygoing.win[3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しだけ。あのベルトにもう一度触れたいの</t>
+          <t xml:space="preserve">ね、思ったより楽しかったわ。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accepted.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3116,14 +3116,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ使ってくれるの。ま、いいけど</t>
+          <t xml:space="preserve">お世話になりました〜。また、どこかで会えたらいいわね</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accepted.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3148,14 +3148,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ必要としてくれるの。じゃあもう少し</t>
+          <t xml:space="preserve">行ってくるわ〜</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defended.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3180,14 +3180,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト持てたものね。十分よ</t>
+          <t xml:space="preserve">ふふ、引き留めてくれて嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defended.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3212,14 +3212,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">潮時ってやつかしら。わかったわ</t>
+          <t xml:space="preserve">残るわ〜。これからもよろしくね</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3244,14 +3244,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">覚悟はできてたわ。最後、よろしくね</t>
+          <t xml:space="preserve">ごめんね〜。引き留めてもらったのに…</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3276,14 +3276,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうよね…ありがとう</t>
+          <t xml:space="preserve">…元気でね〜</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.easygoing.seductive[1]</t>
+          <t xml:space="preserve">default.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3308,14 +3308,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうよね…勝てなくなっちゃったものね</t>
+          <t xml:space="preserve">もう少しやってみようかしら</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">former_champ.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3340,14 +3340,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだチャンピオンよ？ もう少し待って</t>
+          <t xml:space="preserve">もう少しだけ。あのベルトにもう一度触れたいの</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…私が邪魔なの？ ひどいわね</t>
+          <t xml:space="preserve">まだ使ってくれるの。ま、いいけど</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">high_trust.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ元気よ。もう少しやらせて</t>
+          <t xml:space="preserve">まだ必要としてくれるの。じゃあもう少し</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ暴れ足りないわ</t>
+          <t xml:space="preserve">ベルト持てたものね。十分よ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高だったわ。ベルト持てて幸せだった</t>
+          <t xml:space="preserve">潮時ってやつかしら。わかったわ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3500,14 +3500,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトは無理だったけど…楽しかったわ</t>
+          <t xml:space="preserve">覚悟はできてたわ。最後、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3532,14 +3532,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後くらい素直になろうかしら。楽しかったわ</t>
+          <t xml:space="preserve">そうよね…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長かったわ…でもあっという間だった</t>
+          <t xml:space="preserve">そうよね…勝てなくなっちゃったものね</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそ…まだこれからだったのに…</t>
+          <t xml:space="preserve">まだチャンピオンよ？ もう少し待って</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3628,14 +3628,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">参ったわ…これからだったのに…</t>
+          <t xml:space="preserve">あら…私が邪魔なの？ ひどいわね</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3660,14 +3660,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">十分やったわ。いい人生だった</t>
+          <t xml:space="preserve">まだまだ元気よ。もう少しやらせて</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3692,14 +3692,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…ベルト持ったまま終わりなの…</t>
+          <t xml:space="preserve">まだまだ暴れ足りないわ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3724,14 +3724,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわよ~。ここ、結構気に入ってるの♪</t>
+          <t xml:space="preserve">最高だったわ。ベルト持てて幸せだった</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3741,29 +3741,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー♡ さすが社長、太っ腹～♪</t>
+          <t xml:space="preserve">ベルトは無理だったけど…楽しかったわ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3773,29 +3773,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、まあいっか♪ 気持ちは伝わったし♡</t>
+          <t xml:space="preserve">最後くらい素直になろうかしら。楽しかったわ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3805,29 +3805,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、ダメ？ …まあしょうがないかぁ。ちょっと寂しいけど。</t>
+          <t xml:space="preserve">長かったわ…でもあっという間だった</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3837,29 +3837,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B1_young.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長ー♪ {tenure}お給料のことなんだけどさ…もうちょっとだけ♡ ダメ？</t>
+          <t xml:space="preserve">うそ…まだこれからだったのに…</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3869,29 +3869,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、やっぱりダメ？ …いつか上げてね？ 約束よ♡</t>
+          <t xml:space="preserve">参ったわ…これからだったのに…</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3901,29 +3901,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B3_older.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれるの？ うーん…{record}なんかね、新しいこと始めたいなって♪</t>
+          <t xml:space="preserve">十分やったわ。いい人生だった</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3933,29 +3933,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのね…。{tenure}ちょっと新しいことしてみたいなって。…ごめんね。</t>
+          <t xml:space="preserve">あら…ベルト持ったまま終わりなの…</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3965,29 +3965,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、そうなるよね。{tenure_farewell}{rivalry}元気でね～♪</t>
+          <t xml:space="preserve">残るわよ~。ここ、結構気に入ってるの♪</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4012,14 +4012,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね社長…。お金じゃないの。気持ちが決まっちゃったから…。</t>
+          <t xml:space="preserve">やったー♡ さすが社長、太っ腹～♪</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4044,402 +4044,402 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、そこまでしてくれるの？ …じゃあもうちょっといよっかな♪</t>
+          <t xml:space="preserve">んー、まあいっか♪ 気持ちは伝わったし♡</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えー、ダメ？ …まあしょうがないかぁ。ちょっと寂しいけど。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長ー♪ {tenure}お給料のことなんだけどさ…もうちょっとだけ♡ ダメ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えー、やっぱりダメ？ …いつか上げてね？ 約束よ♡</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれるの？ うーん…{record}なんかね、新しいこと始めたいなって♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、あのね…。{tenure}ちょっと新しいことしてみたいなって。…ごめんね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、そうなるよね。{tenure_farewell}{rivalry}元気でね～♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめんね社長…。お金じゃないの。気持ちが決まっちゃったから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え、そこまでしてくれるの？ …じゃあもうちょっといよっかな♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr" s="12">
+      <c r="D124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr" s="2">
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うれしいけど〜、今の子たちが大好きすぎて動けないのよね。
 ごめんね</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr" s="12">
+      <c r="D125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr" s="2">
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんなさいね、今のところが好きなの。
 またね</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あら、スカウト？
 ふふ、聞かせてもらおうかしら</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr" s="12">
+      <c r="D127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr" s="2">
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やった！ 新しい団体ね！
 楽しみだわ</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、いつもと違う感じ。いいわね</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">どうしたのかしら…楽しいって感覚、どこかに行っちゃったわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、やる気が戻ってきたわ。楽しまなくちゃね</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">長かったわ。でもまた楽しくなってきたの</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">defeat.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふふ…なんでかしら、いつもみたいに動けないの</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、治ったはずなのに…調子出ないわ</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">参ったわ…リングが少し怖いの</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">penalty_end.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">怪我は治ったんだけど…なんだか気分が乗らないの</t>
-        </is>
-      </c>
-    </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4449,29 +4449,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
+          <t xml:space="preserve">あら、いつもと違う感じ。いいわね</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4481,29 +4481,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fresh.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4513,29 +4513,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.seductive[1]</t>
+          <t xml:space="preserve">heavy.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4545,29 +4545,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">warm.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4577,29 +4577,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
+          <t xml:space="preserve">どうしたのかしら…楽しいって感覚、どこかに行っちゃったわ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
@@ -4619,19 +4619,19 @@
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
+          <t xml:space="preserve">あら、やる気が戻ってきたわ。楽しまなくちゃね</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4641,29 +4641,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
+          <t xml:space="preserve">長かったわ。でもまた楽しくなってきたの</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4673,29 +4673,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">defeat.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
+          <t xml:space="preserve">ふふ…なんでかしら、いつもみたいに動けないの</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4705,29 +4705,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
+          <t xml:space="preserve">あら、治ったはずなのに…調子出ないわ</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4737,29 +4737,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
+          <t xml:space="preserve">参ったわ…リングが少し怖いの</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4769,29 +4769,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">penalty_end.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
+          <t xml:space="preserve">怪我は治ったんだけど…なんだか気分が乗らないの</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4801,29 +4801,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
+          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4833,29 +4833,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
+          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4865,29 +4865,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
+          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4897,29 +4897,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">mvp.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
+          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4929,29 +4929,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rookie.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
+          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4961,29 +4961,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
+          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4993,29 +4993,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
+          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[3]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[3]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
+          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5057,29 +5057,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
+          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5089,29 +5089,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
+          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[3]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5121,29 +5121,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[3]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
+          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5153,29 +5153,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
+          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5185,29 +5185,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N2.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
+          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5217,29 +5217,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N3.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
+          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5249,29 +5249,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N4.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
+          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5281,29 +5281,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N5_low.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
+          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5313,29 +5313,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
+          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bonus.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5360,14 +5360,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
+          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">camp.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5392,14 +5392,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
+          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
+          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.easygoing.seductive[1]</t>
+          <t xml:space="preserve">encourage.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5456,14 +5456,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
+          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.easygoing.seductive[1]</t>
+          <t xml:space="preserve">faction_decree.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5488,14 +5488,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
+          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">media.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5520,14 +5520,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
+          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5537,12 +5537,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">party.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5552,14 +5552,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
+          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5584,14 +5584,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
+          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5616,14 +5616,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
+          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing.seductive[1]</t>
+          <t xml:space="preserve">trainer.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5648,14 +5648,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
+          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">E1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5680,14 +5680,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
+          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing.seductive[1]</t>
+          <t xml:space="preserve">E6.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5712,14 +5712,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
+          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5744,14 +5744,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
+          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5776,14 +5776,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
+          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
+          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_sns.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
+          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5857,29 +5857,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5889,29 +5889,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S2.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5921,29 +5921,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S3.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5953,29 +5953,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5985,29 +5985,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6017,29 +6017,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S5.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6049,29 +6049,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S6.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6081,29 +6081,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6113,29 +6113,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6177,29 +6177,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6209,29 +6209,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6241,29 +6241,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6273,29 +6273,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6305,29 +6305,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6337,29 +6337,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6369,29 +6369,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
@@ -6416,14 +6416,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
@@ -6448,14 +6448,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
@@ -6480,14 +6480,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
@@ -6512,14 +6512,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
@@ -6544,14 +6544,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6561,29 +6561,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
+          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6593,29 +6593,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
+          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6625,29 +6625,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6657,29 +6657,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">draftJoin.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ?</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6689,29 +6689,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
+          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6721,29 +6721,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">faSigning.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだお楽しみは続くの? いいわね、乗ってあげる</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6753,29 +6753,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6785,29 +6785,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.seductive[2]</t>
+          <t xml:space="preserve">heatSelf.fresh.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6817,29 +6817,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6849,29 +6849,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">heatSelf.warm.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6881,29 +6881,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.seductive[1]</t>
+          <t xml:space="preserve">injury.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6913,29 +6913,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.seductive[2]</t>
+          <t xml:space="preserve">release.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6945,29 +6945,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6977,29 +6977,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.seductive[2]</t>
+          <t xml:space="preserve">scoutGreeting.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
+          <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7009,29 +7009,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7041,29 +7041,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">titleDefense.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7073,29 +7073,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7105,29 +7105,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">titleWin.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるわよね</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7137,29 +7137,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7169,29 +7169,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7201,29 +7201,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい大会だったわ〜</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7233,29 +7233,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になったわね</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7297,29 +7297,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7329,29 +7329,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7361,29 +7361,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
+          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7393,29 +7393,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
+          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7425,29 +7425,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目を集められるなら、いいわね</t>
+          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7457,29 +7457,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
+          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7489,29 +7489,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった!ふふ、最高の舞台で、最高の結末ね♪</t>
+          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7521,29 +7521,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
+          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7553,29 +7553,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7585,29 +7585,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
+          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7617,29 +7617,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
+          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7649,29 +7649,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7681,29 +7681,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
+          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7713,29 +7713,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7745,29 +7745,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7777,29 +7777,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7809,29 +7809,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7841,59 +7841,1499 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだまだお楽しみは続くの? いいわね、乗ってあげる</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、こういう日もあるわよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しい大会だったわ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい経験になったわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">注目を集められるなら、いいわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝っちゃった!ふふ、最高の舞台で、最高の結末ね♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[3]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr" s="2">
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr" s="12">
+      <c r="D278" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.easygoing.seductive[1]</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr" s="2">
+      <c r="E278" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr" s="3">
+      <c r="F278" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
         </is>
       </c>
     </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H235"/>
+  <autoFilter ref="A1:H280"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
@@ -345,7 +345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H321"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -403,7 +403,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -418,7 +418,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.seductive[1]</t>
+          <t xml:space="preserve">atk.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -435,7 +435,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -450,7 +450,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.seductive[2]</t>
+          <t xml:space="preserve">atk.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -467,7 +467,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -482,7 +482,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.seductive[3]</t>
+          <t xml:space="preserve">atk.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -499,7 +499,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.seductive[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.easygoing[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -514,7 +514,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.seductive[4]</t>
+          <t xml:space="preserve">atk.seductive.easygoing[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -531,7 +531,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -546,7 +546,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bigmove.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -563,7 +563,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bigmove.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -595,7 +595,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -610,7 +610,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.seductive[3]</t>
+          <t xml:space="preserve">bigmove.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -627,7 +627,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -642,7 +642,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.seductive[1]</t>
+          <t xml:space="preserve">climax.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -659,7 +659,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -674,7 +674,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.seductive[2]</t>
+          <t xml:space="preserve">climax.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -691,7 +691,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -706,7 +706,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -723,7 +723,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -738,7 +738,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -755,7 +755,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -787,7 +787,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -802,7 +802,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">badWinner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -819,7 +819,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -834,7 +834,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">goodWinner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -851,7 +851,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -866,7 +866,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.seductive[1]</t>
+          <t xml:space="preserve">competition_won.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -883,7 +883,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -898,7 +898,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.seductive[2]</t>
+          <t xml:space="preserve">competition_won.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -915,7 +915,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -930,7 +930,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.seductive[1]</t>
+          <t xml:space="preserve">direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -947,7 +947,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -962,7 +962,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.seductive[2]</t>
+          <t xml:space="preserve">direct.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -979,7 +979,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -994,7 +994,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fa_signing.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -1011,7 +1011,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.seductive[2]</t>
+          <t xml:space="preserve">fa_signing.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1043,7 +1043,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.seductive.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive.hit[1]</t>
+          <t xml:space="preserve">seductive.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1075,7 +1075,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.seductive.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive.hit[2]</t>
+          <t xml:space="preserve">seductive.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1107,7 +1107,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.seductive.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.easygoing.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive.win[1]</t>
+          <t xml:space="preserve">seductive.easygoing.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1139,7 +1139,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.easygoing.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive.win[2]</t>
+          <t xml:space="preserve">seductive.easygoing.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1171,7 +1171,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1203,7 +1203,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1235,7 +1235,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1267,7 +1267,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1299,7 +1299,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1331,7 +1331,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1363,7 +1363,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1395,7 +1395,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1427,7 +1427,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1459,7 +1459,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1491,7 +1491,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1523,7 +1523,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1555,7 +1555,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1587,7 +1587,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1619,7 +1619,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1651,7 +1651,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1683,7 +1683,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.easygoing.seductive[1]</t>
+          <t xml:space="preserve">ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1715,7 +1715,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.easygoing.seductive[1]</t>
+          <t xml:space="preserve">behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1747,7 +1747,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1779,7 +1779,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1811,7 +1811,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1843,7 +1843,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1875,7 +1875,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1907,7 +1907,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1939,7 +1939,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1971,7 +1971,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -2003,7 +2003,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2035,7 +2035,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2067,7 +2067,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2099,7 +2099,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2131,7 +2131,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2163,7 +2163,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2195,7 +2195,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2227,7 +2227,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2259,7 +2259,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2291,7 +2291,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -3091,7 +3091,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accepted.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3123,7 +3123,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.seductive[2]</t>
+          <t xml:space="preserve">accepted.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3155,7 +3155,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defended.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3187,7 +3187,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.seductive[2]</t>
+          <t xml:space="preserve">defended.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3219,7 +3219,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3251,7 +3251,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.seductive[2]</t>
+          <t xml:space="preserve">defense_failed.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3283,7 +3283,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.easygoing.seductive[1]</t>
+          <t xml:space="preserve">default.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3315,7 +3315,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">former_champ.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3347,7 +3347,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3379,7 +3379,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3411,7 +3411,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3443,7 +3443,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3475,7 +3475,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3507,7 +3507,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3539,7 +3539,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.easygoing.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3571,7 +3571,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3603,7 +3603,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3635,7 +3635,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3667,7 +3667,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3699,7 +3699,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3731,7 +3731,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3763,7 +3763,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3795,7 +3795,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3827,7 +3827,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B1_young.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3859,7 +3859,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3891,7 +3891,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B3_older.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3923,7 +3923,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3955,7 +3955,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3987,7 +3987,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4019,7 +4019,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4051,7 +4051,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4083,7 +4083,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4115,7 +4115,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4147,7 +4147,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4172,14 +4172,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれるの？ うーん…{record}なんかね、新しいこと始めたいなって♪</t>
+          <t xml:space="preserve">ふふ、もう引き止めないでくださいね？ 決めちゃったんですから。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4204,14 +4204,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのね…。{tenure}ちょっと新しいことしてみたいなって。…ごめんね。</t>
+          <t xml:space="preserve">さよなら、社長。楽しかった時もあったわ。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4236,14 +4236,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、そうなるよね。{tenure_farewell}{rivalry}元気でね～♪</t>
+          <t xml:space="preserve">聞いてくれるの？ うーん…{record}なんかね、新しいこと始めたいなって♪</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね社長…。お金じゃないの。気持ちが決まっちゃったから…。</t>
+          <t xml:space="preserve">社長、あのね…。{tenure}ちょっと新しいことしてみたいなって。…ごめんね。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4300,14 +4300,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、そこまでしてくれるの？ …じゃあもうちょっといよっかな♪</t>
+          <t xml:space="preserve">あはは、そうなるよね。{tenure_farewell}{rivalry}元気でね～♪</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4317,193 +4317,193 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめんね社長…。お金じゃないの。気持ちが決まっちゃったから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え、そこまでしてくれるの？ …じゃあもうちょっといよっかな♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">blocked.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">blocked.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うれしいけど〜、今の子たちが大好きすぎて動けないのよね。
 ごめんね</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fail.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fail.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんなさいね、今のところが好きなの。
 またね</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">start.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あら、スカウト？
 ふふ、聞かせてもらおうかしら</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">success.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F129" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やった！ 新しい団体ね！
 楽しみだわ</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、いつもと違う感じ。いいわね</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fresh.easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
-        </is>
-      </c>
-    </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4513,29 +4513,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.easygoing.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
+          <t xml:space="preserve">社長〜、私たちの子のこと、ちゃんと可愛がってあげないとダメですよ?</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4545,29 +4545,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
+          <t xml:space="preserve">社長〜、次のメイン、私たちでいかが? 楽しい絵を描けるわよ。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4577,29 +4577,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしたのかしら…楽しいって感覚、どこかに行っちゃったわ</t>
+          <t xml:space="preserve">社長〜、お給料の話、たまには上向きにしてくれないと困りますよ?</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4609,29 +4609,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、やる気が戻ってきたわ。楽しまなくちゃね</t>
+          <t xml:space="preserve">社長〜、私のこと、たまには褒めてくれないと拗ねちゃいますよ?</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4641,29 +4641,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長かったわ。でもまた楽しくなってきたの</t>
+          <t xml:space="preserve">わ、社長ちゃんと聞いてくれてた! ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4673,29 +4673,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんでかしら、いつもみたいに動けないの</t>
+          <t xml:space="preserve">えぇ〜、つれない。まあいいですけど〜。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4705,29 +4705,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、治ったはずなのに…調子出ないわ</t>
+          <t xml:space="preserve">あら、別の形? まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4737,29 +4737,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">参ったわ…リングが少し怖いの</t>
+          <t xml:space="preserve">やった〜、社長ありがとう! 楽しいメインにしますね。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4769,29 +4769,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったんだけど…なんだか気分が乗らないの</t>
+          <t xml:space="preserve">えぇ〜、つれない。まあいいですけど〜。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4801,29 +4801,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
+          <t xml:space="preserve">あら、そっちの形? まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4833,29 +4833,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
+          <t xml:space="preserve">えっホントに〜? 社長ありがとう! みんなに自慢しちゃう。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4865,29 +4865,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
+          <t xml:space="preserve">えぇ〜、つれない〜。まあ次に期待してます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4897,29 +4897,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
+          <t xml:space="preserve">あら、お金の話そらされた〜。でもまあ、ありがと社長。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4929,29 +4929,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
+          <t xml:space="preserve">わ、社長に褒められちゃった〜! 嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4961,29 +4961,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
+          <t xml:space="preserve">えぇ〜、つれない〜。まあいいですけど〜。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4993,29 +4993,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
+          <t xml:space="preserve">あら、別ルート? まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
+          <t xml:space="preserve">あら、気にしてた? ごめん、次は誘うね〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5057,29 +5057,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
+          <t xml:space="preserve">ありがとうございます〜、楽しんできますね。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5089,29 +5089,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
+          <t xml:space="preserve">あら、配慮足りなかった? 気をつけるね〜。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5121,29 +5121,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
+          <t xml:space="preserve">ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5153,29 +5153,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
+          <t xml:space="preserve">えぇ〜、お客さんノッてたのに〜。はい、控えますね。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5185,29 +5185,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜! 引き続き暴れちゃう〜。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5217,29 +5217,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
+          <t xml:space="preserve">あら、ばれちゃった? 明日から出るね〜。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5249,29 +5249,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
+          <t xml:space="preserve">お〜、見逃してくれるの? 社長優しい〜。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5281,29 +5281,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
+          <t xml:space="preserve">あら、私じゃなくて子たち優先? まあ、ありがたいです〜。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5313,29 +5313,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
+          <t xml:space="preserve">あら、バレちゃった? じゃ、お言葉に甘えて〜。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5345,29 +5345,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
+          <t xml:space="preserve">いやいや、まだ大丈夫〜。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5377,29 +5377,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
+          <t xml:space="preserve">あら、メンバー優先? まあ、助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5409,29 +5409,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
+          <t xml:space="preserve">えー、そんな話してた? まあ、注意しとくね〜。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5441,29 +5441,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
+          <t xml:space="preserve">お〜、放っといてくれるんですね〜。ありがと〜。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5473,29 +5473,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
+          <t xml:space="preserve">あら、別ルートで動いてくれるの? ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5505,29 +5505,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
+          <t xml:space="preserve">あら、バレてた? 気をつけますね〜。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5537,29 +5537,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
+          <t xml:space="preserve">（含み笑いで、何も言わなかった）</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5569,29 +5569,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
+          <t xml:space="preserve">あら、別の形? まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5601,29 +5601,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
+          <t xml:space="preserve">あら、これくらい平気なんだけどな〜。じゃ、緩めますね。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5633,29 +5633,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
+          <t xml:space="preserve">お〜、続けていいの? やった〜!</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5665,29 +5665,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
+          <t xml:space="preserve">あら、私じゃなくて子たち? まあ、ありがたいですけどね〜。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.seductive</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5697,29 +5697,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.attack.seductive</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
+          <t xml:space="preserve">仲良しごっこは終わり、でしょ？</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.seductive</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5729,29 +5729,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing.seductive[1]</t>
+          <t xml:space="preserve">easygoing.defend.seductive</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
+          <t xml:space="preserve">ま、仕方ないわね</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.seductive[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5761,29 +5761,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
+          <t xml:space="preserve">あら、いつもと違う感じ。いいわね</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5793,29 +5793,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.easygoing.seductive[1]</t>
+          <t xml:space="preserve">fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5825,29 +5825,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.easygoing.seductive[1]</t>
+          <t xml:space="preserve">heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5857,29 +5857,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5889,29 +5889,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
+          <t xml:space="preserve">どうしたのかしら…楽しいって感覚、どこかに行っちゃったわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5921,29 +5921,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
+          <t xml:space="preserve">あら、やる気が戻ってきたわ。楽しまなくちゃね</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5953,29 +5953,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
+          <t xml:space="preserve">長かったわ。でもまた楽しくなってきたの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5985,29 +5985,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.easygoing.seductive[1]</t>
+          <t xml:space="preserve">defeat.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
+          <t xml:space="preserve">ふふ…なんでかしら、いつもみたいに動けないの</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6017,29 +6017,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.easygoing.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
+          <t xml:space="preserve">あら、治ったはずなのに…調子出ないわ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6049,29 +6049,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.easygoing.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
+          <t xml:space="preserve">参ったわ…リングが少し怖いの</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6081,29 +6081,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
+          <t xml:space="preserve">怪我は治ったんだけど…なんだか気分が乗らないの</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6113,29 +6113,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
+          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.easygoing.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
+          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6177,29 +6177,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
+          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6209,29 +6209,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">mvp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
+          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6241,29 +6241,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rookie.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
+          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6273,29 +6273,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
+          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6305,29 +6305,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
+          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6337,29 +6337,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
+          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6369,29 +6369,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
+          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6401,29 +6401,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6433,29 +6433,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6465,29 +6465,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">N1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6497,29 +6497,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">N2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6529,29 +6529,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">N3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6561,29 +6561,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
+          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6593,29 +6593,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N5_low.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
+          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6625,29 +6625,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6657,29 +6657,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bonus.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6689,29 +6689,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">camp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
+          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6721,29 +6721,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6753,29 +6753,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.seductive[1]</t>
+          <t xml:space="preserve">encourage.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6785,29 +6785,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.easygoing.seductive[1]</t>
+          <t xml:space="preserve">faction_decree.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
+          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6817,29 +6817,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.easygoing.seductive[1]</t>
+          <t xml:space="preserve">media.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
+          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6849,29 +6849,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.easygoing.seductive[1]</t>
+          <t xml:space="preserve">party.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
+          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6881,29 +6881,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6913,29 +6913,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6945,29 +6945,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">trainer.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6977,29 +6977,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing.seductive[1]</t>
+          <t xml:space="preserve">E1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
+          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7009,29 +7009,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">E6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7041,29 +7041,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7073,29 +7073,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7105,29 +7105,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7137,29 +7137,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S_sns.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7169,29 +7169,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7201,29 +7201,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7233,29 +7233,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7297,29 +7297,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7329,29 +7329,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S5.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
+          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7361,29 +7361,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">S6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
+          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7393,29 +7393,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">B1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
+          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7425,29 +7425,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
+          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7457,29 +7457,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
+          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7489,29 +7489,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">B4_brand.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
+          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7521,29 +7521,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
+          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7553,29 +7553,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">B4_fan.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
+          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7585,29 +7585,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
+          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7617,29 +7617,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">B4_gravure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
+          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7649,29 +7649,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
+          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7681,29 +7681,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">B4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
+          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7713,29 +7713,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7745,29 +7745,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7777,29 +7777,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7809,29 +7809,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7841,29 +7841,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7873,29 +7873,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
+          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7905,29 +7905,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
+          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7937,29 +7937,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
+          <t xml:space="preserve">draftInterest.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7969,29 +7969,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8001,29 +8001,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
+          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8033,29 +8033,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">faSigning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ?</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8065,29 +8065,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8097,29 +8097,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">heatSelf.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだお楽しみは続くの? いいわね、乗ってあげる</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8129,29 +8129,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.seductive[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8161,29 +8161,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.seductive[2]</t>
+          <t xml:space="preserve">heatSelf.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8193,29 +8193,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8225,29 +8225,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8257,29 +8257,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8289,29 +8289,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.seductive[2]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
+          <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8321,29 +8321,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8353,29 +8353,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.seductive[2]</t>
+          <t xml:space="preserve">titleDefense.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8417,29 +8417,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.seductive[2]</t>
+          <t xml:space="preserve">titleWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8449,29 +8449,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8481,29 +8481,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるわよね</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8513,29 +8513,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8545,29 +8545,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8577,29 +8577,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい大会だったわ〜</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8609,29 +8609,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になったわね</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8641,29 +8641,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8673,29 +8673,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
+          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8705,29 +8705,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
+          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8737,29 +8737,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
+          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8769,29 +8769,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
+          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8801,29 +8801,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目を集められるなら、いいわね</t>
+          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8833,29 +8833,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
+          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8865,29 +8865,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった!ふふ、最高の舞台で、最高の結末ね♪</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8897,29 +8897,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
+          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8929,29 +8929,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
+          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8961,29 +8961,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8993,29 +8993,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
+          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9025,29 +9025,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
+          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9057,29 +9057,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
+          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9089,29 +9089,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9121,29 +9121,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9153,29 +9153,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9185,29 +9185,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.seductive[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9217,29 +9217,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[3]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9249,29 +9249,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing.seductive[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
+          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9281,29 +9281,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
+          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9313,27 +9313,1339 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだまだお楽しみは続くの? いいわね、乗ってあげる</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、こういう日もあるわよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しい大会だったわ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい経験になったわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">注目を集められるなら、いいわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝っちゃった!ふふ、最高の舞台で、最高の結末ね♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr" s="2">
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr" s="3">
+      <c r="F321" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H280"/>
+  <autoFilter ref="A1:H321"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(蠱惑×お気楽)に該当するキャラクター: 5名</t>
+          <t xml:space="preserve">このタイプ(蠱惑×お気楽)に該当するキャラクター: 7名</t>
         </is>
       </c>
     </row>
@@ -323,15 +323,59 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="12">
         <is>
+          <t xml:space="preserve">穴澤ほのか</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Grappler</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Neutral</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ファンサービス、引き出し上手、野心</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">海老名栞</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Submission</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Babyface</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ファンサービス、ライバル体質、野心</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="12">
+        <is>
           <t xml:space="preserve">愛川明日香</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="2">
+      <c r="B10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Allround</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="2">
+      <c r="C10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Heel</t>
         </is>
@@ -345,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H321"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -460,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合にしましょ?</t>
+          <t xml:space="preserve">いい試合にしましょ？</t>
         </is>
       </c>
     </row>
@@ -844,7 +888,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの声援が聞こえてたわ~♪ 最高の試合だったわね</t>
+          <t xml:space="preserve">みんなの声援が聞こえてたわ〜♪ 最高の試合だったわね</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1208,7 @@
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切ったこと、ちょっとは後悔してくれてるかしら?</t>
+          <t xml:space="preserve">切ったこと、ちょっとは後悔してくれてるかしら？</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1592,7 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからはわたしの時間よ♪</t>
+          <t xml:space="preserve">ここからは私の時間よ♪</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1624,7 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}〜ごめんね…わたし、決められちゃった…</t>
+          <t xml:space="preserve">{partner}〜ごめんね…私、決められちゃった…</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2488,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、あの人とやりたいの。だめ?</t>
+          <t xml:space="preserve">社長〜、あの人とやりたいの。だめ？</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2552,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とやらせて? わがままよね、私。</t>
+          <t xml:space="preserve">あの人とやらせて？ わがままよね、私。</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2776,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、私? ふふ、いいわよー、遊びましょ。</t>
+          <t xml:space="preserve">え、私？ ふふ、いいわよー、遊びましょ。</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2808,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、呼ばれたら行くわよ。そういうものでしょ?</t>
+          <t xml:space="preserve">ま、呼ばれたら行くわよ。そういうものでしょ？</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2872,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかずかぁ。…ま、いいんじゃない?</t>
+          <t xml:space="preserve">決着つかずかぁ。…ま、いいんじゃない？</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2904,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決まらなかったわね。お茶でも飲む?</t>
+          <t xml:space="preserve">決まらなかったわね。お茶でも飲む？</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3064,7 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、勝っちゃった。ごめんね?</t>
+          <t xml:space="preserve">ふふ、勝っちゃった。ごめんね？</t>
         </is>
       </c>
     </row>
@@ -3980,7 +4024,7 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわよ~。ここ、結構気に入ってるの♪</t>
+          <t xml:space="preserve">残るわよ〜。ここ、結構気に入ってるの♪</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4572,7 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、私たちの子のこと、ちゃんと可愛がってあげないとダメですよ?</t>
+          <t xml:space="preserve">社長〜、私たちの子のこと、ちゃんと可愛がってあげないとダメですよ？</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4604,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、次のメイン、私たちでいかが? 楽しい絵を描けるわよ。</t>
+          <t xml:space="preserve">社長〜、次のメイン、私たちでいかが？ 楽しい絵を描けるわよ。</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4636,7 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、お給料の話、たまには上向きにしてくれないと困りますよ?</t>
+          <t xml:space="preserve">社長〜、お給料の話、たまには上向きにしてくれないと困りますよ？</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4668,7 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、私のこと、たまには褒めてくれないと拗ねちゃいますよ?</t>
+          <t xml:space="preserve">社長〜、私のこと、たまには褒めてくれないと拗ねちゃいますよ？</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4700,7 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長ちゃんと聞いてくれてた! ありがとうございます〜。</t>
+          <t xml:space="preserve">わ、社長ちゃんと聞いてくれてた！ ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4764,7 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形? まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">あら、別の形？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4796,7 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長ありがとう! 楽しいメインにしますね。</t>
+          <t xml:space="preserve">やった〜、社長ありがとう！ 楽しいメインにしますね。</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4860,7 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そっちの形? まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">あら、そっちの形？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4892,7 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっホントに〜? 社長ありがとう! みんなに自慢しちゃう。</t>
+          <t xml:space="preserve">えっホントに〜？ 社長ありがとう！ みんなに自慢しちゃう。</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4988,7 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長に褒められちゃった〜! 嬉しいです。</t>
+          <t xml:space="preserve">わ、社長に褒められちゃった〜！ 嬉しいです。</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5052,7 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別ルート? まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">あら、別ルート？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5084,7 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、気にしてた? ごめん、次は誘うね〜。</t>
+          <t xml:space="preserve">あら、気にしてた？ ごめん、次は誘うね〜。</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5148,7 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、配慮足りなかった? 気をつけるね〜。</t>
+          <t xml:space="preserve">あら、配慮足りなかった？ 気をつけるね〜。</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5244,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長わかってる〜! 引き続き暴れちゃう〜。</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れちゃう〜。</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5276,7 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ばれちゃった? 明日から出るね〜。</t>
+          <t xml:space="preserve">あら、ばれちゃった？ 明日から出るね〜。</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5308,7 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、見逃してくれるの? 社長優しい〜。</t>
+          <t xml:space="preserve">お〜、見逃してくれるの？ 社長優しい〜。</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5340,7 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、私じゃなくて子たち優先? まあ、ありがたいです〜。</t>
+          <t xml:space="preserve">あら、私じゃなくて子たち優先？ まあ、ありがたいです〜。</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5372,7 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、バレちゃった? じゃ、お言葉に甘えて〜。</t>
+          <t xml:space="preserve">あら、バレちゃった？ じゃ、お言葉に甘えて〜。</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5436,7 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、メンバー優先? まあ、助かります〜。</t>
+          <t xml:space="preserve">あら、メンバー優先？ まあ、助かります〜。</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5468,7 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、そんな話してた? まあ、注意しとくね〜。</t>
+          <t xml:space="preserve">えー、そんな話してた？ まあ、注意しとくね〜。</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5532,7 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別ルートで動いてくれるの? ありがとうございます〜。</t>
+          <t xml:space="preserve">あら、別ルートで動いてくれるの？ ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5564,7 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、バレてた? 気をつけますね〜。</t>
+          <t xml:space="preserve">あら、バレてた？ 気をつけますね〜。</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5628,7 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形? まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">あら、別の形？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5692,7 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、続けていいの? やった〜!</t>
+          <t xml:space="preserve">お〜、続けていいの？ やった〜！</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5724,7 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、私じゃなくて子たち? まあ、ありがたいですけどね〜。</t>
+          <t xml:space="preserve">あら、私じゃなくて子たち？ まあ、ありがたいですけどね〜。</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6147,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6118,7 +6162,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6128,14 +6172,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
+          <t xml:space="preserve">みんなで勝つと、祝福も何倍も楽しいのね。</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6150,7 +6194,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6160,14 +6204,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
+          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6182,7 +6226,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.easygoing[1]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6192,14 +6236,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
+          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6214,7 +6258,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6224,14 +6268,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
+          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6246,7 +6290,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.easygoing[1]</t>
+          <t xml:space="preserve">mvp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6256,14 +6300,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
+          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6273,12 +6317,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">rookie.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6288,14 +6332,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
+          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6305,12 +6349,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">springTagChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6320,14 +6364,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
+          <t xml:space="preserve">相棒と一緒だと、勝つまでの時間まで楽しめちゃうの。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6342,7 +6386,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[3]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6352,14 +6396,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
+          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6369,12 +6413,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6384,14 +6428,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
+          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6401,12 +6445,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6416,14 +6460,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
+          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6438,7 +6482,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[3]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6448,14 +6492,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
+          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6465,29 +6509,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
+          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6497,29 +6541,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
+          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6534,7 +6578,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6544,14 +6588,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
+          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6566,7 +6610,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6576,14 +6620,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
+          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6598,7 +6642,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6608,14 +6652,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
+          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6630,7 +6674,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6640,14 +6684,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
+          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6657,29 +6701,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N5_low.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
+          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6689,29 +6733,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
+          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6726,7 +6770,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bonus.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6736,14 +6780,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
+          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6758,7 +6802,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.easygoing[1]</t>
+          <t xml:space="preserve">camp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6768,14 +6812,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
+          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6790,7 +6834,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.seductive.easygoing[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6800,14 +6844,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
+          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6822,7 +6866,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.easygoing[1]</t>
+          <t xml:space="preserve">encourage.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6832,14 +6876,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
+          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6854,7 +6898,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6864,14 +6908,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
+          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6886,7 +6930,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.easygoing[1]</t>
+          <t xml:space="preserve">media.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6896,14 +6940,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
+          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6918,7 +6962,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.easygoing[1]</t>
+          <t xml:space="preserve">party.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6928,14 +6972,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
+          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6950,7 +6994,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.easygoing[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6960,14 +7004,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
+          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6977,12 +7021,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6992,14 +7036,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
+          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7009,12 +7053,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">trainer.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7024,14 +7068,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
+          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7046,7 +7090,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.easygoing[1]</t>
+          <t xml:space="preserve">E1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7056,14 +7100,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
+          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7078,7 +7122,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.easygoing[2]</t>
+          <t xml:space="preserve">E6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7088,14 +7132,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
+          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7110,7 +7154,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7120,14 +7164,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
+          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7142,7 +7186,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7152,14 +7196,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
+          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7174,7 +7218,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7184,14 +7228,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
+          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7206,7 +7250,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_sns.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7216,14 +7260,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
+          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7238,7 +7282,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7248,14 +7292,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
+          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7270,7 +7314,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7280,14 +7324,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
+          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7302,7 +7346,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7312,14 +7356,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
+          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7334,7 +7378,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7344,14 +7388,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
+          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7366,7 +7410,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7376,14 +7420,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
+          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7393,12 +7437,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S5.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7408,14 +7452,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
+          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7425,12 +7469,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7440,14 +7484,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
+          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7462,7 +7506,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7472,14 +7516,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
+          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7494,7 +7538,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7504,14 +7548,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
+          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7526,7 +7570,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7536,14 +7580,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
+          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7558,7 +7602,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7568,14 +7612,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
+          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7590,7 +7634,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7600,14 +7644,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
+          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7622,7 +7666,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7632,14 +7676,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
+          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7654,7 +7698,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7664,14 +7708,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
+          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7686,7 +7730,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7696,14 +7740,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
+          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7713,29 +7757,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7745,29 +7789,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7777,7 +7821,7 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
@@ -7792,14 +7836,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7809,7 +7853,7 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
@@ -7824,14 +7868,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7841,7 +7885,7 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
@@ -7856,14 +7900,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7873,12 +7917,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7888,14 +7932,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7905,12 +7949,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7920,14 +7964,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7942,7 +7986,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7952,14 +7996,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7974,7 +8018,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7984,14 +8028,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8006,7 +8050,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8016,14 +8060,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8038,7 +8082,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8048,14 +8092,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8070,7 +8114,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8080,14 +8124,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">あら、悪くない話じゃない♪　…ええ、お世話になるわね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8102,7 +8146,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8112,14 +8156,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8134,7 +8178,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8144,14 +8188,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8166,7 +8210,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8176,14 +8220,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8198,7 +8242,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8208,14 +8252,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8230,7 +8274,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8240,14 +8284,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8262,7 +8306,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8272,14 +8316,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8294,7 +8338,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8304,14 +8348,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8326,7 +8370,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8336,14 +8380,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8358,7 +8402,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8368,14 +8412,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">ふうん、私に目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8390,7 +8434,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8400,14 +8444,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8422,7 +8466,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8432,14 +8476,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8449,12 +8493,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8464,14 +8508,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8481,12 +8525,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8496,14 +8540,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8513,7 +8557,7 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
@@ -8528,14 +8572,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8545,7 +8589,7 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
@@ -8560,14 +8604,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8577,7 +8621,7 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
@@ -8592,14 +8636,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8609,7 +8653,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
@@ -8624,14 +8668,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8641,29 +8685,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8673,29 +8717,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8710,7 +8754,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8720,14 +8764,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8742,7 +8786,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8752,14 +8796,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
+          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8774,7 +8818,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8784,14 +8828,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
+          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8806,7 +8850,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8816,14 +8860,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
+          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8838,7 +8882,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8848,14 +8892,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
+          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8870,7 +8914,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8880,14 +8924,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
+          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8902,7 +8946,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8912,14 +8956,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
+          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8934,7 +8978,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8944,14 +8988,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8966,7 +9010,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8976,14 +9020,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
+          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8998,7 +9042,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9008,14 +9052,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
+          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9030,7 +9074,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9040,14 +9084,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9062,7 +9106,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9072,14 +9116,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
+          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9094,7 +9138,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9104,14 +9148,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
+          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9126,7 +9170,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9136,14 +9180,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
+          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9158,7 +9202,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9168,14 +9212,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9190,7 +9234,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9200,14 +9244,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9222,7 +9266,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9232,14 +9276,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
+          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9254,7 +9298,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9264,14 +9308,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
+          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9281,12 +9325,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9296,14 +9340,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9313,29 +9357,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
+          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9345,29 +9389,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ?</t>
+          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9382,7 +9426,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9392,14 +9436,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
+          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9414,7 +9458,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9424,14 +9468,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだお楽しみは続くの? いいわね、乗ってあげる</t>
+          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9446,7 +9490,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9456,14 +9500,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
+          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9478,7 +9522,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9488,14 +9532,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
+          <t xml:space="preserve">まだまだお楽しみは続くの？ いいわね、乗ってあげる</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9505,12 +9549,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">survivor.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9520,14 +9564,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
+          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9537,12 +9581,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">survivor.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9552,14 +9596,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
+          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9574,7 +9618,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.easygoing[1]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9584,14 +9628,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
+          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9606,7 +9650,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.easygoing[2]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9616,14 +9660,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
+          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9638,7 +9682,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.easygoing[1]</t>
+          <t xml:space="preserve">defiant.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9648,14 +9692,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
+          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9670,7 +9714,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.easygoing[2]</t>
+          <t xml:space="preserve">defiant.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9680,14 +9724,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
+          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9697,12 +9741,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9712,14 +9756,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
+          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9729,12 +9773,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9744,14 +9788,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
+          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9766,7 +9810,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9776,14 +9820,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
+          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9798,7 +9842,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9808,14 +9852,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるわよね</t>
+          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9830,7 +9874,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">postLose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9840,14 +9884,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
+          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9862,7 +9906,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">postLose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9872,14 +9916,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
+          <t xml:space="preserve">ま、こういう日もあるわよね</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9894,7 +9938,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9904,14 +9948,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい大会だったわ〜</t>
+          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9926,7 +9970,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9936,14 +9980,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になったわね</t>
+          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9958,7 +10002,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">postWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9968,14 +10012,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
+          <t xml:space="preserve">楽しい大会だったわ〜</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9990,7 +10034,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">postWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10000,14 +10044,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
+          <t xml:space="preserve">いい経験になったわね</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10022,7 +10066,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10032,14 +10076,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
+          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10054,7 +10098,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10064,14 +10108,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
+          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10086,7 +10130,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10096,14 +10140,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
+          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10118,7 +10162,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10128,14 +10172,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目を集められるなら、いいわね</t>
+          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10145,12 +10189,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">summon.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10160,14 +10204,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
+          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10177,12 +10221,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">summon.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10192,14 +10236,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった!ふふ、最高の舞台で、最高の結末ね♪</t>
+          <t xml:space="preserve">注目を集められるなら、いいわね</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10209,7 +10253,7 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
@@ -10224,14 +10268,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
+          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10241,12 +10285,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10256,14 +10300,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
+          <t xml:space="preserve">勝っちゃった！ふふ、最高の舞台で、最高の結末ね♪</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10273,7 +10317,7 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
@@ -10288,14 +10332,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
+          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10305,7 +10349,7 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
@@ -10320,14 +10364,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
+          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10337,12 +10381,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10352,14 +10396,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
+          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10369,12 +10413,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10384,14 +10428,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
+          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10406,7 +10450,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10416,14 +10460,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10438,7 +10482,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.easygoing[2]</t>
+          <t xml:space="preserve">result_lose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10448,14 +10492,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10465,12 +10509,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">result_win.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10480,14 +10524,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10497,12 +10541,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">result_win.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10512,14 +10556,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10534,7 +10578,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[3]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10544,14 +10588,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10561,29 +10605,29 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
+          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10593,59 +10637,123 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾ってくれるなんて。…優しいのね、ここ</t>
+          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、悪くない話じゃない♪　…ええ、お世話になるわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr" s="2">
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr" s="12">
+      <c r="D323" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr" s="2">
+      <c r="E323" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ふうん、あたしに目をつけたんだ。…お目が高いね</t>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふうん、私に目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H321"/>
+  <autoFilter ref="A1:H323"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4031,7 +4031,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.seductive.easygoing[1]</t>
+          <t xml:space="preserve">decline_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー♡ さすが社長、太っ腹～♪</t>
+          <t xml:space="preserve">はいはい、了解。……お店のランクを一つ落とすだけの話でしょ？</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.seductive.easygoing[1]</t>
+          <t xml:space="preserve">decline_hold.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4088,14 +4088,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、まあいっか♪ 気持ちは伝わったし♡</t>
+          <t xml:space="preserve">えっ、据え置き？　……やだ、ちょっと嬉しい♪　……損な人ね、あなた。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.seductive.easygoing[1]</t>
+          <t xml:space="preserve">decline_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、ダメ？ …まあしょうがないかぁ。ちょっと寂しいけど。</t>
+          <t xml:space="preserve">あー、来ると思ってた♪　……で、どのくらい下がるの？　先に言っちゃって。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.seductive.easygoing[1]</t>
+          <t xml:space="preserve">decline_strict.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4152,14 +4152,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長ー♪ {tenure}お給料のことなんだけどさ…もうちょっとだけ♡ ダメ？</t>
+          <t xml:space="preserve">うわ、きっちり回収するのね♪　……あなたのそういうとこ、嫌いじゃなかったのに。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.seductive.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4184,14 +4184,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、やっぱりダメ？ …いつか上げてね？ 約束よ♡</t>
+          <t xml:space="preserve">はい、契約成立。……自分で言った値段だもの、文句なんて出るわけないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4216,14 +4216,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、もう引き止めないでくださいね？ 決めちゃったんですから。</t>
+          <t xml:space="preserve">え、そのまま？　……ちょっと、それ反則よ♪　……せっかく格好つけたのに。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.easygoing[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4248,14 +4248,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さよなら、社長。楽しかった時もあったわ。</t>
+          <t xml:space="preserve">はい、正直に言うね。……もう昔の値段の女じゃないの。下げていいわよ、そのぶん長く置いて？</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.seductive.easygoing[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4280,14 +4280,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれるの？ うーん…{record}なんかね、新しいこと始めたいなって♪</t>
+          <t xml:space="preserve">やったー♡ さすが社長、太っ腹～♪</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのね…。{tenure}ちょっと新しいことしてみたいなって。…ごめんね。</t>
+          <t xml:space="preserve">んー、まあいっか♪ 気持ちは伝わったし♡</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.seductive.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4344,14 +4344,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、そうなるよね。{tenure_farewell}{rivalry}元気でね～♪</t>
+          <t xml:space="preserve">えー、ダメ？ …まあしょうがないかぁ。ちょっと寂しいけど。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.seductive.easygoing[1]</t>
+          <t xml:space="preserve">raise_open.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4376,14 +4376,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね社長…。お金じゃないの。気持ちが決まっちゃったから…。</t>
+          <t xml:space="preserve">社長ー♪ {tenure}お給料のことなんだけどさ…もうちょっとだけ♡ ダメ？</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.seductive.easygoing[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4408,370 +4408,370 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、そこまでしてくれるの？ …じゃあもうちょっといよっかな♪</t>
+          <t xml:space="preserve">えー、やっぱりダメ？ …いつか上げてね？ 約束よ♡</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、もう引き止めないでくださいね？ 決めちゃったんですから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さよなら、社長。楽しかった時もあったわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれるの？ うーん…{record}なんかね、新しいこと始めたいなって♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、あのね…。{tenure}ちょっと新しいことしてみたいなって。…ごめんね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、そうなるよね。{tenure_farewell}{rivalry}元気でね～♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ごめんね社長…。お金じゃないの。気持ちが決まっちゃったから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え、そこまでしてくれるの？ …じゃあもうちょっといよっかな♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うれしいけど〜、今の子たちが大好きすぎて動けないのよね。
 ごめんね</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ごめんなさいね、今のところが好きなの。
 またね</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="D135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr" s="2">
+      <c r="E135" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr" s="3">
+      <c r="F135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あら、スカウト？
 ふふ、聞かせてもらおうかしら</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr" s="12">
+      <c r="D136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr" s="2">
+      <c r="E136" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr" s="3">
+      <c r="F136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やった！ 新しい団体ね！
 楽しみだわ</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、私たちの子のこと、ちゃんと可愛がってあげないとダメですよ？</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、次のメイン、私たちでいかが？ 楽しい絵を描けるわよ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、お給料の話、たまには上向きにしてくれないと困りますよ？</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長〜、私のこと、たまには褒めてくれないと拗ねちゃいますよ？</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わ、社長ちゃんと聞いてくれてた！ ありがとうございます〜。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">えぇ〜、つれない。まあいいですけど〜。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、別の形？ まあ、ありがとうございます〜。</t>
-        </is>
-      </c>
-    </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長ありがとう！ 楽しいメインにしますね。</t>
+          <t xml:space="preserve">社長〜、私たちの子のこと、ちゃんと可愛がってあげないとダメですよ？</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4828,14 +4828,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、つれない。まあいいですけど〜。</t>
+          <t xml:space="preserve">社長〜、次のメイン、私たちでいかが？ 楽しい絵を描けるわよ。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そっちの形？ まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">社長〜、お給料の話、たまには上向きにしてくれないと困りますよ？</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっホントに〜？ 社長ありがとう！ みんなに自慢しちゃう。</t>
+          <t xml:space="preserve">社長〜、私のこと、たまには褒めてくれないと拗ねちゃいますよ？</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、つれない〜。まあ次に期待してます。</t>
+          <t xml:space="preserve">わ、社長ちゃんと聞いてくれてた！ ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4956,14 +4956,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お金の話そらされた〜。でもまあ、ありがと社長。</t>
+          <t xml:space="preserve">えぇ〜、つれない。まあいいですけど〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長に褒められちゃった〜！ 嬉しいです。</t>
+          <t xml:space="preserve">あら、別の形？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、つれない〜。まあいいですけど〜。</t>
+          <t xml:space="preserve">やった〜、社長ありがとう！ 楽しいメインにしますね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -5052,14 +5052,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別ルート？ まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">えぇ〜、つれない。まあいいですけど〜。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、気にしてた？ ごめん、次は誘うね〜。</t>
+          <t xml:space="preserve">あら、そっちの形？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜、楽しんできますね。</t>
+          <t xml:space="preserve">えっホントに〜？ 社長ありがとう！ みんなに自慢しちゃう。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、配慮足りなかった？ 気をつけるね〜。</t>
+          <t xml:space="preserve">えぇ〜、つれない〜。まあ次に期待してます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5180,14 +5180,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。</t>
+          <t xml:space="preserve">あら、お金の話そらされた〜。でもまあ、ありがと社長。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5212,14 +5212,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、お客さんノッてたのに〜。はい、控えますね。</t>
+          <t xml:space="preserve">わ、社長に褒められちゃった〜！ 嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れちゃう〜。</t>
+          <t xml:space="preserve">えぇ〜、つれない〜。まあいいですけど〜。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5276,14 +5276,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ばれちゃった？ 明日から出るね〜。</t>
+          <t xml:space="preserve">あら、別ルート？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、見逃してくれるの？ 社長優しい〜。</t>
+          <t xml:space="preserve">あら、気にしてた？ ごめん、次は誘うね〜。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5340,14 +5340,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、私じゃなくて子たち優先？ まあ、ありがたいです〜。</t>
+          <t xml:space="preserve">ありがとうございます〜、楽しんできますね。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、バレちゃった？ じゃ、お言葉に甘えて〜。</t>
+          <t xml:space="preserve">あら、配慮足りなかった？ 気をつけるね〜。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5404,14 +5404,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやいや、まだ大丈夫〜。</t>
+          <t xml:space="preserve">ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5436,14 +5436,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、メンバー優先？ まあ、助かります〜。</t>
+          <t xml:space="preserve">えぇ〜、お客さんノッてたのに〜。はい、控えますね。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、そんな話してた？ まあ、注意しとくね〜。</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れちゃう〜。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、放っといてくれるんですね〜。ありがと〜。</t>
+          <t xml:space="preserve">あら、ばれちゃった？ 明日から出るね〜。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5532,14 +5532,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別ルートで動いてくれるの？ ありがとうございます〜。</t>
+          <t xml:space="preserve">お〜、見逃してくれるの？ 社長優しい〜。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5564,14 +5564,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、バレてた？ 気をつけますね〜。</t>
+          <t xml:space="preserve">あら、私じゃなくて子たち優先？ まあ、ありがたいです〜。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5596,14 +5596,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（含み笑いで、何も言わなかった）</t>
+          <t xml:space="preserve">あら、バレちゃった？ じゃ、お言葉に甘えて〜。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形？ まあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">いやいや、まだ大丈夫〜。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5660,14 +5660,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、これくらい平気なんだけどな〜。じゃ、緩めますね。</t>
+          <t xml:space="preserve">あら、メンバー優先？ まあ、助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5692,14 +5692,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お〜、続けていいの？ やった〜！</t>
+          <t xml:space="preserve">えー、そんな話してた？ まあ、注意しとくね〜。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5724,14 +5724,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、私じゃなくて子たち？ まあ、ありがたいですけどね〜。</t>
+          <t xml:space="preserve">お〜、放っといてくれるんですね〜。ありがと〜。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5756,14 +5756,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しごっこは終わり、でしょ？</t>
+          <t xml:space="preserve">あら、別ルートで動いてくれるの？ ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5788,14 +5788,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、仕方ないわね</t>
+          <t xml:space="preserve">あら、バレてた？ 気をつけますね〜。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5805,29 +5805,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、いつもと違う感じ。いいわね</t>
+          <t xml:space="preserve">（含み笑いで、何も言わなかった）</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5837,29 +5837,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
+          <t xml:space="preserve">あら、別の形？ まあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5869,29 +5869,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
+          <t xml:space="preserve">あら、これくらい平気なんだけどな〜。じゃ、緩めますね。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5901,29 +5901,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
+          <t xml:space="preserve">お〜、続けていいの？ やった〜！</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5933,29 +5933,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしたのかしら…楽しいって感覚、どこかに行っちゃったわ</t>
+          <t xml:space="preserve">あら、私じゃなくて子たち？ まあ、ありがたいですけどね〜。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.seductive</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5965,29 +5965,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.attack.seductive</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、やる気が戻ってきたわ。楽しまなくちゃね</t>
+          <t xml:space="preserve">仲良しごっこは終わり、でしょ？</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.seductive</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5997,29 +5997,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.defend.seductive</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長かったわ。でもまた楽しくなってきたの</t>
+          <t xml:space="preserve">ま、仕方ないわね</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.easygoing[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -6044,14 +6044,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんでかしら、いつもみたいに動けないの</t>
+          <t xml:space="preserve">あら、いつもと違う感じ。いいわね</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.easygoing[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.seductive.easygoing[1]</t>
+          <t xml:space="preserve">fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、治ったはずなのに…調子出ないわ</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.easygoing[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">参ったわ…リングが少し怖いの</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.easygoing[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.seductive.easygoing[1]</t>
+          <t xml:space="preserve">warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6140,14 +6140,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったんだけど…なんだか気分が乗らないの</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6157,29 +6157,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで勝つと、祝福も何倍も楽しいのね。</t>
+          <t xml:space="preserve">どうしたのかしら…楽しいって感覚、どこかに行っちゃったわ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6189,29 +6189,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
+          <t xml:space="preserve">あら、やる気が戻ってきたわ。楽しまなくちゃね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6221,29 +6221,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
+          <t xml:space="preserve">長かったわ。でもまた楽しくなってきたの</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6253,29 +6253,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.easygoing[1]</t>
+          <t xml:space="preserve">defeat.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
+          <t xml:space="preserve">ふふ…なんでかしら、いつもみたいに動けないの</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
+          <t xml:space="preserve">あら、治ったはずなのに…調子出ないわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6317,29 +6317,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.easygoing[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
+          <t xml:space="preserve">参ったわ…リングが少し怖いの</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6349,29 +6349,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒と一緒だと、勝つまでの時間まで楽しめちゃうの。</t>
+          <t xml:space="preserve">怪我は治ったんだけど…なんだか気分が乗らないの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
+          <t xml:space="preserve">みんなで勝つと、祝福も何倍も楽しいのね。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">bestMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
+          <t xml:space="preserve">楽しかったわ。久しぶりに全部忘れて夢中になれた</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[3]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
+          <t xml:space="preserve">チャンピオン。いい響きね。似合うでしょう？</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
+          <t xml:space="preserve">楽しい日々だったわ。全部、宝物。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">mvp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6524,14 +6524,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
+          <t xml:space="preserve">最優秀選手ですって。…似合うと思わない？</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[3]</t>
+          <t xml:space="preserve">rookie.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
+          <t xml:space="preserve">あら、嬉しいサプライズ。来年はもっと驚かせてあげる</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6573,29 +6573,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">springTagChampion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
+          <t xml:space="preserve">相棒と一緒だと、勝つまでの時間まで楽しめちゃうの。</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
+          <t xml:space="preserve">ふふっ、ドームって素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
+          <t xml:space="preserve">のんびり楽しませてもらうわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6669,29 +6669,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
+          <t xml:space="preserve">気楽に、でもちゃんと色気は出すわよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6701,29 +6701,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
+          <t xml:space="preserve">ふふっ、満員って素敵な響きね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6733,29 +6733,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
+          <t xml:space="preserve">皆様、私たちを愛してくれたのね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6765,29 +6765,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
+          <t xml:space="preserve">こんな幸せな夜、他にないわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6797,29 +6797,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
+          <t xml:space="preserve">あら、急にいろいろ掴めちゃったかも</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6829,29 +6829,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
+          <t xml:space="preserve">あの人と一緒にいると楽しいの。最高のパートナーね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6861,29 +6861,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
+          <t xml:space="preserve">ちょっと疲れちゃったかしら。少し休めば大丈夫よ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6893,29 +6893,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
+          <t xml:space="preserve">ファンの方が喜んでくれると、もっと見せたくなるわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6925,29 +6925,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N5_low.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
+          <t xml:space="preserve">ふふ…もういいかなって、少し思っちゃった</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6957,29 +6957,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
+          <t xml:space="preserve">ふふ…なんでもないわ。気にしないで</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bonus.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
+          <t xml:space="preserve">あら嬉しい。何に使おうかしら</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.easygoing[1]</t>
+          <t xml:space="preserve">camp.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
+          <t xml:space="preserve">合宿楽しみ〜。みんなで頑張りましょ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.easygoing[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
+          <t xml:space="preserve">見てくれてたのね。嬉しいわ。もう少し頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">encourage.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
+          <t xml:space="preserve">ふふ、元気出ちゃった。やってみるわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
+          <t xml:space="preserve">あら残念。いい集まりだったのに</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.easygoing[1]</t>
+          <t xml:space="preserve">media.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
+          <t xml:space="preserve">テレビ？ みんなに見てもらえるのね。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.easygoing[2]</t>
+          <t xml:space="preserve">party.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7196,14 +7196,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
+          <t xml:space="preserve">ふふ、みんないい顔してるわね</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.easygoing[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
+          <t xml:space="preserve">バカンスね。リフレッシュして戻るわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.easygoing[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7260,14 +7260,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
+          <t xml:space="preserve">ふふ、こんなに大事にされたら、頑張らなきゃ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">trainer.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7292,14 +7292,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
+          <t xml:space="preserve">マンツーマンなんて贅沢ね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">E1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7324,14 +7324,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
+          <t xml:space="preserve">ファンのみんなにもっと見てもらえるのね。嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.easygoing[1]</t>
+          <t xml:space="preserve">E6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7356,14 +7356,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
+          <t xml:space="preserve">他所からお誘いが来ちゃった。ちょっと嬉しいかも</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
+          <t xml:space="preserve">ふふ…今日はサボっちゃおうかな…</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7420,14 +7420,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
+          <t xml:space="preserve">練習ねぇ…今日は、遠慮しておくわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7452,14 +7452,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
+          <t xml:space="preserve">（笑顔が消え、「ねえ…ちょっと聞いてよ」と同僚に愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S_sns.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
+          <t xml:space="preserve">（SNSに「最近ね、ちょっと考えることがあるの」と珍しく素の投稿）</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
+          <t xml:space="preserve">ベルト、欲しくなっちゃった。挑戦させてくれない？</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
+          <t xml:space="preserve">あの人との試合、組んでくれない？ 決着つけたいの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S3.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7580,14 +7580,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
+          <t xml:space="preserve">ごめんね、ちょっと限界みたい。休ませてくれる？</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
+          <t xml:space="preserve">ぶっちゃけ、不満があるの。ちゃんと話しましょう？</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
+          <t xml:space="preserve">ふふ…ううん、なんでもないの（笑顔のまま、目だけが冷えている）</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S5.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7676,14 +7676,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
+          <t xml:space="preserve">特訓したいの。もっと強くなりたくて</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">S6.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7708,14 +7708,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
+          <t xml:space="preserve">後輩の子たち、かわいいわよね。面倒見させてもらえない？</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
+          <t xml:space="preserve">あら、やっちゃった…でもすぐ治すわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7772,14 +7772,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
+          <t xml:space="preserve">あの人とはもう無理。顔も見たくないわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
+          <t xml:space="preserve">ケンカ売ってきたのは向こうよ？ 買ってあげるわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7821,29 +7821,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
+          <t xml:space="preserve">コラボ商品か…どんなのになるかな♡</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7853,29 +7853,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
+          <t xml:space="preserve">CM出演か…どんな自分が映るか楽しみ♡</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7885,29 +7885,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">ファンに会いに行くの？ 嬉しいな♡</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7917,29 +7917,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">ランウェイ！ 絶対楽しい！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7949,29 +7949,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">グラビア？ 任せておいてよ♡</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7981,29 +7981,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
+          <t xml:space="preserve">バラエティか〜。楽しそう！ 見ててよ♡</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -8013,29 +8013,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.seductive.easygoing[1]</t>
+          <t xml:space="preserve">B4.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
+          <t xml:space="preserve">テレビに出れるの？ 嬉しい。もっと見てもらえるわね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8067,7 +8067,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8124,14 +8124,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、悪くない話じゃない♪　…ええ、お世話になるわね</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8156,14 +8156,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
+          <t xml:space="preserve">片がついた相手なのにね。…目に入るとイラつくわ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.seductive.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
+          <t xml:space="preserve">終わったって聞いたわ。…誰が決めたのかしらね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.seductive.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
+          <t xml:space="preserve">一緒に楽しい団体を作りましょう？</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
+          <t xml:space="preserve">ふふ、よろしくね。楽しくやりましょ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8348,14 +8348,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
+          <t xml:space="preserve">あら、悪くない話じゃない♪　…ええ、お世話になるわね</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
+          <t xml:space="preserve">新しい場所ね。楽しみだわ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふうん、私に目をつけたんだ。…お目が高いね</t>
+          <t xml:space="preserve">よろしくね。楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">今日の体、いい感じ。…もっと動きたい気分なの</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8476,14 +8476,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">体が重いの。…今日は、やるだけ損な気がするわ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.warm.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8508,14 +8508,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">今日はちょっと乗らないの。…なんでかしらね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">injury.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8540,14 +8540,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">ちょっと休憩ね？ すぐ戻るから寂しがらないで</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">release.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8579,7 +8579,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8611,7 +8611,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8636,14 +8636,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
+          <t xml:space="preserve">ふうん、私に目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8749,29 +8749,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8781,29 +8781,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
+          <t xml:space="preserve">ふふ、縁がなかったみたいね。お元気で</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8813,29 +8813,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
+          <t xml:space="preserve">お邪魔するわね。短い間だけど楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8845,29 +8845,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
+          <t xml:space="preserve">今日は負けちゃったわね。次はもっと輝くから見ていて</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8877,29 +8877,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
+          <t xml:space="preserve">防衛って地味に見える？ ふふ、そんなことないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8909,29 +8909,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
+          <t xml:space="preserve">負けちゃったわね…でも私は私。立ち上がるわ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8941,29 +8941,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
+          <t xml:space="preserve">ベルトが似合うのは私だけでしょ？ ふふ</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8988,14 +8988,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもねぇ…</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9020,14 +9020,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
+          <t xml:space="preserve">あら〜、最近ちょっと素っ気ないわね</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
+          <t xml:space="preserve">ん〜、なんとなく空気が変わった感じ？</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9084,14 +9084,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
+          <t xml:space="preserve">一緒にいて飽きないわ〜</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9116,14 +9116,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
+          <t xml:space="preserve">最高の相棒よ〜。ずっと一緒にいたいわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9148,14 +9148,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">一緒にいると、なんでも上手くいっちゃうの</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9180,14 +9180,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
+          <t xml:space="preserve">熱い関係も一段落ね。ちょっと寂しいわ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃないものね〜</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9244,14 +9244,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
+          <t xml:space="preserve">いい勝負になりそうね〜。燃えてきちゃった</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
+          <t xml:space="preserve">ふふ、負けたくないわ〜</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9308,14 +9308,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そうはいないわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9340,14 +9340,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
+          <t xml:space="preserve">ふふ、考えるだけで自然と気合が入っちゃう</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
+          <t xml:space="preserve">この試合が一番楽しいの。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9404,14 +9404,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
+          <t xml:space="preserve">運命のライバルね〜。最高だわ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9421,29 +9421,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいわ！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9453,29 +9453,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ？</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいのよね〜</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9485,29 +9485,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
+          <t xml:space="preserve">さすがにこれは…笑えないわね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9517,29 +9517,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだお楽しみは続くの？ いいわね、乗ってあげる</t>
+          <t xml:space="preserve">ふふ…なんて笑ってる場合じゃないわ、これ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9549,29 +9549,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするのよね…</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9581,29 +9581,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.seductive[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
+          <t xml:space="preserve">まぁ大丈夫…よね？ ちょっと不安だけど</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9613,29 +9613,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
+          <t xml:space="preserve">あらら、魔法が解けちゃったわ〜。でも楽しかった</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
+          <t xml:space="preserve">満身創痍だけど…最後の舞台、楽しんじゃおうかな</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
+          <t xml:space="preserve">ぼろぼろの私、でも一番いいところで残ったの。悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
+          <t xml:space="preserve">相手は誰が来るのかしら。何人でも、退屈しなさそうね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
+          <t xml:space="preserve">まだまだお楽しみは続くの？ いいわね、乗ってあげる</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.easygoing[2]</t>
+          <t xml:space="preserve">survivor.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
+          <t xml:space="preserve">一人、落としちゃった。…ふぅ、でもまだ物足りないの。次、来ていいわよ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
+          <t xml:space="preserve">survivor.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
+          <t xml:space="preserve">まだ立ってるの。次の子、こっちおいで。まだまだ楽しめそうだし</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
+          <t xml:space="preserve">三人で勝つって、こんなに気持ちいいのね。最高の夜だわ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9884,14 +9884,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
+          <t xml:space="preserve">仲間と分かち合う勝利……悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">defiant.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういう日もあるわよね</t>
+          <t xml:space="preserve">個人賞ね……悪くないけど、一人で浸る夜じゃないわ。次は三人で</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">defiant.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9948,14 +9948,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
+          <t xml:space="preserve">今日は笑えないかな。次はチームごと勝って、本気の乾杯よ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9980,14 +9980,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
+          <t xml:space="preserve">何人来ても退屈しなかったわ。こういう夜は、汗も悪くないでしょ？</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10012,14 +10012,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい大会だったわ〜</t>
+          <t xml:space="preserve">次から次へ……でも、最後に残るのはいつもこっち。楽しかったわ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.seductive.easygoing[2]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10044,14 +10044,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になったわね</t>
+          <t xml:space="preserve">あらあら、優勝しちゃったわ。素敵</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
+          <t xml:space="preserve">champion.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10076,14 +10076,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
+          <t xml:space="preserve">ふふ、最高の気分。ご褒美ちょうだいね</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
+          <t xml:space="preserve">postLose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10108,14 +10108,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
+          <t xml:space="preserve">あらら、残念。でもまた来年があるわ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
+          <t xml:space="preserve">postLose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10140,14 +10140,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
+          <t xml:space="preserve">ま、こういう日もあるわよね</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10172,14 +10172,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
+          <t xml:space="preserve">あら、勝っちゃった。ラッキー</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10204,14 +10204,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
+          <t xml:space="preserve">いい感じ。次も楽しみましょう</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.seductive.easygoing[2]</t>
+          <t xml:space="preserve">postWin.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10236,14 +10236,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目を集められるなら、いいわね</t>
+          <t xml:space="preserve">楽しい大会だったわ〜</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">postWin.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10268,14 +10268,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
+          <t xml:space="preserve">いい経験になったわね</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10300,14 +10300,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった！ふふ、最高の舞台で、最高の結末ね♪</t>
+          <t xml:space="preserve">決勝かあ。最高の舞台じゃない</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10332,14 +10332,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
+          <t xml:space="preserve">あと一つ。楽しんでいきましょう</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10364,14 +10364,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
+          <t xml:space="preserve">さてと、楽しませてもらうわね</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10381,12 +10381,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10396,14 +10396,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
+          <t xml:space="preserve">リラックス、リラックス。……でも本気よ</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">summon.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10428,14 +10428,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
+          <t xml:space="preserve">あら〜、ラッキー。いい舞台じゃない</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.easygoing[1]</t>
+          <t xml:space="preserve">summon.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10460,14 +10460,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
+          <t xml:space="preserve">注目を集められるなら、いいわね</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10492,14 +10492,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
+          <t xml:space="preserve">あなたと戦えるの、楽しみだったわ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10524,14 +10524,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+          <t xml:space="preserve">勝っちゃった！ふふ、最高の舞台で、最高の結末ね♪</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10556,14 +10556,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+          <t xml:space="preserve">ね、一緒に遊ばない？ …本気のやつ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10588,14 +10588,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+          <t xml:space="preserve">退屈してたの。相手してくれるかしら</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[2]</t>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+          <t xml:space="preserve">あらあら、怖がっちゃって。可愛い</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[3]</t>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10652,14 +10652,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+          <t xml:space="preserve">残念。もっと楽しめると思ったのに</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10669,29 +10669,29 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.seductive.easygoing[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
+          <t xml:space="preserve">あらら、ダメだったわね。ま、次があるわ</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10701,59 +10701,283 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.seductive.easygoing[2]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、悪くない話じゃない♪　…ええ、お世話になるわね</t>
+          <t xml:space="preserve">負けちゃった。…でも、引きずらないわ</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝っちゃった。楽しかったわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい対抗戦だったわね。また遊びましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、勝っちゃった。うちの団体、いいでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、楽しかったわ〜。またやりたいわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、楽しかったわ。またいつでもどうぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の景色ね。みんなのおかげだわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、悪くない話じゃない♪　…ええ、お世話になるわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr" s="2">
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr" s="12">
+      <c r="D330" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.easygoing[1]</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr" s="2">
+      <c r="E330" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr" s="3">
+      <c r="F330" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ふうん、私に目をつけたんだ。…お目が高いね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H323"/>
+  <autoFilter ref="A1:H330"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×お気楽.xlsx
@@ -2488,7 +2488,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、あの人とやりたいの。だめ？</t>
+          <t xml:space="preserve">社長〜、三人であちらへ行きたいの。だめ？</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ社長、あの人と当てて。お願い。</t>
+          <t xml:space="preserve">ねえ社長、三人であの団体に当てて。お願い。</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とやらせて？ わがままよね、私。</t>
+          <t xml:space="preserve">三人であちらへ行かせて？ わがままよね、私。</t>
         </is>
       </c>
     </row>
